--- a/LMT.xlsx
+++ b/LMT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E351FAEE-D77D-41FC-8ACE-AFD46A53E8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B09F17-B3B0-40C3-98EE-DB66C521A3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{EA792E1E-3BA0-4584-A29C-9504A225675A}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{EA792E1E-3BA0-4584-A29C-9504A225675A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="122">
   <si>
     <t xml:space="preserve">Lockhead Martin </t>
   </si>
@@ -400,6 +400,9 @@
   </si>
   <si>
     <t>Equity &amp; Liabilties</t>
+  </si>
+  <si>
+    <t>EPS</t>
   </si>
 </sst>
 </file>
@@ -410,13 +413,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -574,35 +583,39 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -961,7 +974,7 @@
         <v>4</v>
       </c>
       <c r="K2" s="3">
-        <v>475.99</v>
+        <v>652.46</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
@@ -987,7 +1000,7 @@
       </c>
       <c r="K4" s="3">
         <f>K2*K3</f>
-        <v>113456.02584797</v>
+        <v>155519.06263738</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -1019,7 +1032,7 @@
       </c>
       <c r="K7" s="3">
         <f>K4-K5+K6</f>
-        <v>130048.16784797001</v>
+        <v>172111.20463738</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
@@ -1288,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9725CA57-4E24-4CA5-A0F0-6B7F19F9F5C3}">
-  <dimension ref="A1:T305"/>
+  <dimension ref="A1:T308"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -1534,7 +1547,9 @@
       <c r="Q10" s="18">
         <v>27474</v>
       </c>
-      <c r="R10" s="18"/>
+      <c r="R10" s="18">
+        <v>28618</v>
+      </c>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
     </row>
@@ -1563,7 +1578,9 @@
       <c r="Q11" s="18">
         <v>11253</v>
       </c>
-      <c r="R11" s="18"/>
+      <c r="R11" s="18">
+        <v>12682</v>
+      </c>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
     </row>
@@ -1592,7 +1609,9 @@
       <c r="Q12" s="18">
         <v>16239</v>
       </c>
-      <c r="R12" s="18"/>
+      <c r="R12" s="18">
+        <v>17264</v>
+      </c>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
     </row>
@@ -1605,7 +1624,6 @@
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
       <c r="K13" s="18"/>
@@ -1621,7 +1639,9 @@
       <c r="Q13" s="18">
         <v>12605</v>
       </c>
-      <c r="R13" s="18"/>
+      <c r="R13" s="18">
+        <v>12479</v>
+      </c>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
     </row>
@@ -1650,7 +1670,9 @@
       <c r="Q14" s="18">
         <v>56265</v>
       </c>
-      <c r="R14" s="18"/>
+      <c r="R14" s="18">
+        <v>59277</v>
+      </c>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
     </row>
@@ -1679,7 +1701,9 @@
       <c r="Q15" s="18">
         <v>11306</v>
       </c>
-      <c r="R15" s="18"/>
+      <c r="R15" s="18">
+        <v>11766</v>
+      </c>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
     </row>
@@ -1720,7 +1744,9 @@
         <f>SUM(Q14:Q15)</f>
         <v>67571</v>
       </c>
-      <c r="R16" s="18"/>
+      <c r="R16" s="19">
+        <v>71043</v>
+      </c>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
     </row>
@@ -1752,50 +1778,56 @@
         <f>50206+10027+92-1233</f>
         <v>59092</v>
       </c>
-      <c r="R17" s="18"/>
+      <c r="R17" s="18">
+        <v>64113</v>
+      </c>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B18" s="1" t="s">
+    <row r="18" spans="1:20" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="19">
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22">
         <f t="shared" ref="L18:P18" si="1">L16-L17</f>
         <v>0</v>
       </c>
-      <c r="M18" s="19">
+      <c r="M18" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N18" s="19">
+      <c r="N18" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O18" s="19">
+      <c r="O18" s="22">
         <f t="shared" si="1"/>
         <v>9061</v>
       </c>
-      <c r="P18" s="19">
+      <c r="P18" s="22">
         <f t="shared" si="1"/>
         <v>8287</v>
       </c>
-      <c r="Q18" s="19">
+      <c r="Q18" s="22">
         <f>Q16-Q17</f>
         <v>8479</v>
       </c>
-      <c r="R18" s="18"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
+      <c r="R18" s="22">
+        <f>R16-R17</f>
+        <v>6930</v>
+      </c>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
@@ -1822,50 +1854,56 @@
       <c r="Q19" s="18">
         <v>28</v>
       </c>
-      <c r="R19" s="18"/>
+      <c r="R19" s="18">
+        <v>83</v>
+      </c>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B20" s="1" t="s">
+    <row r="20" spans="1:20" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="19">
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22">
         <f t="shared" ref="L20:P20" si="2">L18+L19</f>
         <v>0</v>
       </c>
-      <c r="M20" s="19">
+      <c r="M20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N20" s="19">
+      <c r="N20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O20" s="19">
+      <c r="O20" s="22">
         <f t="shared" si="2"/>
         <v>9123</v>
       </c>
-      <c r="P20" s="19">
+      <c r="P20" s="22">
         <f t="shared" si="2"/>
         <v>8348</v>
       </c>
-      <c r="Q20" s="19">
+      <c r="Q20" s="22">
         <f>Q18+Q19</f>
         <v>8507</v>
       </c>
-      <c r="R20" s="18"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
+      <c r="R20" s="22">
+        <f>R18+R19</f>
+        <v>7013</v>
+      </c>
+      <c r="S20" s="23"/>
+      <c r="T20" s="23"/>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
@@ -1895,7 +1933,10 @@
         <f>-916+443+64</f>
         <v>-409</v>
       </c>
-      <c r="R21" s="18"/>
+      <c r="R21" s="18">
+        <f>-1036+62+181</f>
+        <v>-793</v>
+      </c>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
     </row>
@@ -1936,7 +1977,10 @@
         <f>Q20+Q21</f>
         <v>8098</v>
       </c>
-      <c r="R22" s="18"/>
+      <c r="R22" s="18">
+        <f>R20+R21</f>
+        <v>6220</v>
+      </c>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
     </row>
@@ -1965,151 +2009,145 @@
       <c r="Q23" s="18">
         <v>1178</v>
       </c>
-      <c r="R23" s="18"/>
+      <c r="R23" s="18">
+        <v>884</v>
+      </c>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B24" s="1" t="s">
+    <row r="24" spans="1:20" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="19">
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22">
         <f t="shared" ref="L24:P24" si="4">L22-L23</f>
         <v>0</v>
       </c>
-      <c r="M24" s="19">
+      <c r="M24" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N24" s="19">
+      <c r="N24" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O24" s="19">
+      <c r="O24" s="22">
         <f t="shared" si="4"/>
         <v>6315</v>
       </c>
-      <c r="P24" s="19">
+      <c r="P24" s="22">
         <f t="shared" si="4"/>
         <v>5732</v>
       </c>
-      <c r="Q24" s="19">
+      <c r="Q24" s="22">
         <f>Q22-Q23</f>
         <v>6920</v>
       </c>
-      <c r="R24" s="18"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="18"/>
-      <c r="R25" s="18"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B26" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="20" t="e">
-        <f t="shared" ref="M26:P26" si="5">M16/L16-1</f>
+      <c r="R24" s="22">
+        <f>R22-R23</f>
+        <v>5336</v>
+      </c>
+      <c r="S24" s="23"/>
+      <c r="T24" s="23"/>
+    </row>
+    <row r="25" spans="1:20" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22"/>
+      <c r="R25" s="22"/>
+      <c r="S25" s="23"/>
+      <c r="T25" s="23"/>
+    </row>
+    <row r="26" spans="1:20" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2"/>
+      <c r="B26" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="23" t="e">
+        <f t="shared" ref="O26:Q26" si="5">+O24/O27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N26" s="20" t="e">
+      <c r="P26" s="23">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O26" s="20" t="e">
+        <v>21.736822146378461</v>
+      </c>
+      <c r="Q26" s="23">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P26" s="20">
-        <f t="shared" si="5"/>
-        <v>-1.5810512499254248E-2</v>
-      </c>
-      <c r="Q26" s="20">
-        <f>Q16/P16-1</f>
-        <v>2.4051285160038738E-2</v>
-      </c>
-      <c r="R26" s="18"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B27" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="20" t="e">
-        <f t="shared" ref="M27:P27" si="6">M18/M16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N27" s="20" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O27" s="20">
-        <f t="shared" si="6"/>
-        <v>0.13515005071296463</v>
-      </c>
-      <c r="P27" s="20">
-        <f t="shared" si="6"/>
-        <v>0.12559105237633367</v>
-      </c>
-      <c r="Q27" s="20">
-        <f>Q18/Q16</f>
-        <v>0.125482825472466</v>
-      </c>
-      <c r="R27" s="18"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
+        <v>27.646823811426287</v>
+      </c>
+      <c r="R26" s="23">
+        <f>+R24/R27</f>
+        <v>22.39194292908099</v>
+      </c>
+      <c r="S26" s="23"/>
+      <c r="T26" s="23"/>
+    </row>
+    <row r="27" spans="1:20" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="2"/>
+      <c r="B27" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22">
+        <v>263.7</v>
+      </c>
+      <c r="Q27" s="22">
+        <v>250.3</v>
+      </c>
+      <c r="R27" s="22">
+        <v>238.3</v>
+      </c>
+      <c r="S27" s="23"/>
+      <c r="T27" s="23"/>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
@@ -2120,69 +2158,60 @@
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
       <c r="L28" s="18"/>
-      <c r="M28" s="20" t="e">
-        <f t="shared" ref="M28:P28" si="7">M20/M16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N28" s="20" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O28" s="20">
-        <f t="shared" si="7"/>
-        <v>0.13607481653839271</v>
-      </c>
-      <c r="P28" s="20">
-        <f t="shared" si="7"/>
-        <v>0.12651551891367604</v>
-      </c>
-      <c r="Q28" s="20">
-        <f>Q20/Q16</f>
-        <v>0.12589720442201535</v>
-      </c>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
       <c r="R28" s="18"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B29" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="20" t="e">
-        <f t="shared" ref="M29:P29" si="8">M23/M22</f>
+      <c r="B29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="24" t="e">
+        <f t="shared" ref="M29:P29" si="6">M16/L16-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N29" s="20" t="e">
-        <f t="shared" si="8"/>
+      <c r="N29" s="24" t="e">
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O29" s="20">
-        <f t="shared" si="8"/>
-        <v>0.16357615894039734</v>
-      </c>
-      <c r="P29" s="20">
-        <f t="shared" si="8"/>
-        <v>0.14191616766467066</v>
-      </c>
-      <c r="Q29" s="20">
-        <f>Q23/Q22</f>
-        <v>0.14546801679427018</v>
-      </c>
-      <c r="R29" s="18"/>
+      <c r="O29" s="24" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P29" s="24">
+        <f t="shared" si="6"/>
+        <v>-1.5810512499254248E-2</v>
+      </c>
+      <c r="Q29" s="24">
+        <f>Q16/P16-1</f>
+        <v>2.4051285160038738E-2</v>
+      </c>
+      <c r="R29" s="24">
+        <f>R16/Q16-1</f>
+        <v>5.1382989744120922E-2</v>
+      </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B30" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
       <c r="E30" s="18"/>
@@ -2193,21 +2222,36 @@
       <c r="J30" s="18"/>
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="18"/>
+      <c r="M30" s="20" t="e">
+        <f t="shared" ref="M30:P30" si="7">M18/M16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N30" s="20" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O30" s="20">
+        <f t="shared" si="7"/>
+        <v>0.13515005071296463</v>
+      </c>
+      <c r="P30" s="20">
+        <f t="shared" si="7"/>
+        <v>0.12559105237633367</v>
+      </c>
+      <c r="Q30" s="20">
+        <f>Q18/Q16</f>
+        <v>0.125482825472466</v>
+      </c>
+      <c r="R30" s="20">
+        <f>R18/R16</f>
+        <v>9.7546556310966592E-2</v>
+      </c>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A31" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>97</v>
+      <c r="B31" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
@@ -2219,18 +2263,36 @@
       <c r="J31" s="18"/>
       <c r="K31" s="18"/>
       <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="18"/>
-      <c r="R31" s="18"/>
+      <c r="M31" s="20" t="e">
+        <f t="shared" ref="M31:P31" si="8">M20/M16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N31" s="20" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O31" s="20">
+        <f t="shared" si="8"/>
+        <v>0.13607481653839271</v>
+      </c>
+      <c r="P31" s="20">
+        <f t="shared" si="8"/>
+        <v>0.12651551891367604</v>
+      </c>
+      <c r="Q31" s="20">
+        <f>Q20/Q16</f>
+        <v>0.12589720442201535</v>
+      </c>
+      <c r="R31" s="20">
+        <f>R20/R16</f>
+        <v>9.8714862829553926E-2</v>
+      </c>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C32" s="18"/>
       <c r="D32" s="18"/>
@@ -2242,23 +2304,34 @@
       <c r="J32" s="18"/>
       <c r="K32" s="18"/>
       <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18">
-        <v>2547</v>
-      </c>
-      <c r="Q32" s="18">
-        <v>1442</v>
-      </c>
-      <c r="R32" s="18"/>
+      <c r="M32" s="20" t="e">
+        <f t="shared" ref="M32:P32" si="9">M23/M22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N32" s="20" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O32" s="20">
+        <f t="shared" si="9"/>
+        <v>0.16357615894039734</v>
+      </c>
+      <c r="P32" s="20">
+        <f t="shared" si="9"/>
+        <v>0.14191616766467066</v>
+      </c>
+      <c r="Q32" s="20">
+        <f>Q23/Q22</f>
+        <v>0.14546801679427018</v>
+      </c>
+      <c r="R32" s="20">
+        <f>R23/R22</f>
+        <v>0.14212218649517686</v>
+      </c>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B33" s="2" t="s">
-        <v>100</v>
-      </c>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
@@ -2272,19 +2345,18 @@
       <c r="M33" s="18"/>
       <c r="N33" s="18"/>
       <c r="O33" s="18"/>
-      <c r="P33" s="18">
-        <v>2505</v>
-      </c>
-      <c r="Q33" s="18">
-        <v>2132</v>
-      </c>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="18"/>
       <c r="R33" s="18"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B34" s="2" t="s">
-        <v>101</v>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A34" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>
@@ -2299,19 +2371,15 @@
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
       <c r="O34" s="18"/>
-      <c r="P34" s="18">
-        <v>12318</v>
-      </c>
-      <c r="Q34" s="18">
-        <v>13183</v>
-      </c>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="18"/>
       <c r="R34" s="18"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
     </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
@@ -2327,18 +2395,18 @@
       <c r="N35" s="18"/>
       <c r="O35" s="18"/>
       <c r="P35" s="18">
-        <v>3088</v>
+        <v>2547</v>
       </c>
       <c r="Q35" s="18">
-        <v>3132</v>
+        <v>1442</v>
       </c>
       <c r="R35" s="18"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
     </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
@@ -2354,18 +2422,18 @@
       <c r="N36" s="18"/>
       <c r="O36" s="18"/>
       <c r="P36" s="18">
-        <v>533</v>
+        <v>2505</v>
       </c>
       <c r="Q36" s="18">
-        <v>632</v>
+        <v>2132</v>
       </c>
       <c r="R36" s="18"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B37" s="1" t="s">
-        <v>104</v>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
@@ -2376,37 +2444,23 @@
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
       <c r="K37" s="18"/>
-      <c r="L37" s="19">
-        <f t="shared" ref="L37:P37" si="9">SUM(L32:L36)</f>
-        <v>0</v>
-      </c>
-      <c r="M37" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="N37" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O37" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P37" s="19">
-        <f t="shared" si="9"/>
-        <v>20991</v>
-      </c>
-      <c r="Q37" s="19">
-        <f>SUM(Q32:Q36)</f>
-        <v>20521</v>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18">
+        <v>12318</v>
+      </c>
+      <c r="Q37" s="18">
+        <v>13183</v>
       </c>
       <c r="R37" s="18"/>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C38" s="18"/>
       <c r="D38" s="18"/>
@@ -2422,18 +2476,18 @@
       <c r="N38" s="18"/>
       <c r="O38" s="18"/>
       <c r="P38" s="18">
-        <v>7975</v>
+        <v>3088</v>
       </c>
       <c r="Q38" s="18">
-        <v>8370</v>
+        <v>3132</v>
       </c>
       <c r="R38" s="18"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C39" s="18"/>
       <c r="D39" s="18"/>
@@ -2449,18 +2503,18 @@
       <c r="N39" s="18"/>
       <c r="O39" s="18"/>
       <c r="P39" s="18">
-        <v>10780</v>
+        <v>533</v>
       </c>
       <c r="Q39" s="18">
-        <v>10799</v>
+        <v>632</v>
       </c>
       <c r="R39" s="18"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
     </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B40" s="2" t="s">
-        <v>107</v>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="C40" s="18"/>
       <c r="D40" s="18"/>
@@ -2471,23 +2525,37 @@
       <c r="I40" s="18"/>
       <c r="J40" s="18"/>
       <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="18"/>
-      <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
-      <c r="P40" s="18">
-        <v>2459</v>
-      </c>
-      <c r="Q40" s="18">
-        <v>2212</v>
+      <c r="L40" s="19">
+        <f t="shared" ref="L40:P40" si="10">SUM(L35:L39)</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N40" s="19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O40" s="19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P40" s="19">
+        <f t="shared" si="10"/>
+        <v>20991</v>
+      </c>
+      <c r="Q40" s="19">
+        <f>SUM(Q35:Q39)</f>
+        <v>20521</v>
       </c>
       <c r="R40" s="18"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
     </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C41" s="18"/>
       <c r="D41" s="18"/>
@@ -2503,18 +2571,18 @@
       <c r="N41" s="18"/>
       <c r="O41" s="18"/>
       <c r="P41" s="18">
-        <v>3744</v>
+        <v>7975</v>
       </c>
       <c r="Q41" s="18">
-        <v>2953</v>
+        <v>8370</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C42" s="18"/>
       <c r="D42" s="18"/>
@@ -2530,18 +2598,18 @@
       <c r="N42" s="18"/>
       <c r="O42" s="18"/>
       <c r="P42" s="18">
-        <v>6931</v>
+        <v>10780</v>
       </c>
       <c r="Q42" s="18">
-        <v>7601</v>
+        <v>10799</v>
       </c>
       <c r="R42" s="18"/>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B43" s="1" t="s">
-        <v>109</v>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B43" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="C43" s="18"/>
       <c r="D43" s="18"/>
@@ -2552,35 +2620,24 @@
       <c r="I43" s="18"/>
       <c r="J43" s="18"/>
       <c r="K43" s="18"/>
-      <c r="L43" s="19">
-        <f t="shared" ref="L43:P43" si="10">SUM(L38:L42)</f>
-        <v>0</v>
-      </c>
-      <c r="M43" s="19">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="N43" s="19">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O43" s="19">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P43" s="19">
-        <f t="shared" si="10"/>
-        <v>31889</v>
-      </c>
-      <c r="Q43" s="19">
-        <f>SUM(Q38:Q42)</f>
-        <v>31935</v>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18">
+        <v>2459</v>
+      </c>
+      <c r="Q43" s="18">
+        <v>2212</v>
       </c>
       <c r="R43" s="18"/>
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B44" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="C44" s="18"/>
       <c r="D44" s="18"/>
       <c r="E44" s="18"/>
@@ -2594,14 +2651,19 @@
       <c r="M44" s="18"/>
       <c r="N44" s="18"/>
       <c r="O44" s="18"/>
-      <c r="P44" s="18"/>
+      <c r="P44" s="18">
+        <v>3744</v>
+      </c>
+      <c r="Q44" s="18">
+        <v>2953</v>
+      </c>
       <c r="R44" s="18"/>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
-        <v>110</v>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B45" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="C45" s="18"/>
       <c r="D45" s="18"/>
@@ -2612,35 +2674,24 @@
       <c r="I45" s="18"/>
       <c r="J45" s="18"/>
       <c r="K45" s="18"/>
-      <c r="L45" s="19">
-        <f t="shared" ref="L45:P45" si="11">L37+L43</f>
-        <v>0</v>
-      </c>
-      <c r="M45" s="19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="N45" s="19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="O45" s="19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P45" s="19">
-        <f t="shared" si="11"/>
-        <v>52880</v>
-      </c>
-      <c r="Q45" s="19">
-        <f>Q37+Q43</f>
-        <v>52456</v>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18">
+        <v>6931</v>
+      </c>
+      <c r="Q45" s="18">
+        <v>7601</v>
       </c>
       <c r="R45" s="18"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3"/>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="C46" s="18"/>
       <c r="D46" s="18"/>
       <c r="E46" s="18"/>
@@ -2650,20 +2701,35 @@
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
       <c r="K46" s="18"/>
-      <c r="L46" s="18"/>
-      <c r="M46" s="18"/>
-      <c r="N46" s="18"/>
-      <c r="O46" s="18"/>
-      <c r="P46" s="18"/>
-      <c r="Q46" s="18"/>
+      <c r="L46" s="19">
+        <f t="shared" ref="L46:P46" si="11">SUM(L41:L45)</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="19">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N46" s="19">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O46" s="19">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="P46" s="19">
+        <f t="shared" si="11"/>
+        <v>31889</v>
+      </c>
+      <c r="Q46" s="19">
+        <f>SUM(Q41:Q45)</f>
+        <v>31935</v>
+      </c>
       <c r="R46" s="18"/>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B47" s="2" t="s">
-        <v>111</v>
-      </c>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C47" s="18"/>
       <c r="D47" s="18"/>
       <c r="E47" s="18"/>
@@ -2677,19 +2743,14 @@
       <c r="M47" s="18"/>
       <c r="N47" s="18"/>
       <c r="O47" s="18"/>
-      <c r="P47" s="18">
-        <v>2117</v>
-      </c>
-      <c r="Q47" s="18">
-        <v>2312</v>
-      </c>
+      <c r="P47" s="18"/>
       <c r="R47" s="18"/>
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B48" s="2" t="s">
-        <v>116</v>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B48" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C48" s="18"/>
       <c r="D48" s="18"/>
@@ -2700,24 +2761,35 @@
       <c r="I48" s="18"/>
       <c r="J48" s="18"/>
       <c r="K48" s="18"/>
-      <c r="L48" s="18"/>
-      <c r="M48" s="18"/>
-      <c r="N48" s="18"/>
-      <c r="O48" s="18"/>
-      <c r="P48" s="18">
-        <v>3075</v>
-      </c>
-      <c r="Q48" s="18">
-        <v>3133</v>
+      <c r="L48" s="19">
+        <f t="shared" ref="L48:P48" si="12">L40+L46</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="19">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="N48" s="19">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O48" s="19">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P48" s="19">
+        <f t="shared" si="12"/>
+        <v>52880</v>
+      </c>
+      <c r="Q48" s="19">
+        <f>Q40+Q46</f>
+        <v>52456</v>
       </c>
       <c r="R48" s="18"/>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B49" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="C49" s="18"/>
       <c r="D49" s="18"/>
       <c r="E49" s="18"/>
@@ -2731,19 +2803,15 @@
       <c r="M49" s="18"/>
       <c r="N49" s="18"/>
       <c r="O49" s="18"/>
-      <c r="P49" s="18">
-        <v>8488</v>
-      </c>
-      <c r="Q49" s="18">
-        <v>9190</v>
-      </c>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="18"/>
       <c r="R49" s="18"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C50" s="18"/>
       <c r="D50" s="18"/>
@@ -2759,10 +2827,10 @@
       <c r="N50" s="18"/>
       <c r="O50" s="18"/>
       <c r="P50" s="18">
-        <v>118</v>
+        <v>2117</v>
       </c>
       <c r="Q50" s="18">
-        <v>168</v>
+        <v>2312</v>
       </c>
       <c r="R50" s="18"/>
       <c r="S50" s="3"/>
@@ -2770,7 +2838,7 @@
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C51" s="18"/>
       <c r="D51" s="18"/>
@@ -2786,18 +2854,18 @@
       <c r="N51" s="18"/>
       <c r="O51" s="18"/>
       <c r="P51" s="18">
-        <v>2089</v>
+        <v>3075</v>
       </c>
       <c r="Q51" s="18">
-        <v>2134</v>
+        <v>3133</v>
       </c>
       <c r="R51" s="18"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
-        <v>114</v>
+      <c r="B52" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="C52" s="18"/>
       <c r="D52" s="18"/>
@@ -2808,29 +2876,15 @@
       <c r="I52" s="18"/>
       <c r="J52" s="18"/>
       <c r="K52" s="18"/>
-      <c r="L52" s="19">
-        <f t="shared" ref="L52:P52" si="12">SUM(L47:L51)</f>
-        <v>0</v>
-      </c>
-      <c r="M52" s="19">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N52" s="19">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O52" s="19">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="P52" s="19">
-        <f t="shared" si="12"/>
-        <v>15887</v>
-      </c>
-      <c r="Q52" s="19">
-        <f>SUM(Q47:Q51)</f>
-        <v>16937</v>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="18">
+        <v>8488</v>
+      </c>
+      <c r="Q52" s="18">
+        <v>9190</v>
       </c>
       <c r="R52" s="18"/>
       <c r="S52" s="3"/>
@@ -2838,7 +2892,7 @@
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="C53" s="18"/>
       <c r="D53" s="18"/>
@@ -2854,10 +2908,10 @@
       <c r="N53" s="18"/>
       <c r="O53" s="18"/>
       <c r="P53" s="18">
-        <v>15429</v>
+        <v>118</v>
       </c>
       <c r="Q53" s="18">
-        <v>17291</v>
+        <v>168</v>
       </c>
       <c r="R53" s="18"/>
       <c r="S53" s="3"/>
@@ -2865,7 +2919,7 @@
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C54" s="18"/>
       <c r="D54" s="18"/>
@@ -2881,18 +2935,18 @@
       <c r="N54" s="18"/>
       <c r="O54" s="18"/>
       <c r="P54" s="18">
-        <v>5472</v>
+        <v>2089</v>
       </c>
       <c r="Q54" s="18">
-        <v>6162</v>
+        <v>2134</v>
       </c>
       <c r="R54" s="18"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B55" s="2" t="s">
-        <v>103</v>
+      <c r="B55" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C55" s="18"/>
       <c r="D55" s="18"/>
@@ -2903,15 +2957,29 @@
       <c r="I55" s="18"/>
       <c r="J55" s="18"/>
       <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
-      <c r="M55" s="18"/>
-      <c r="N55" s="18"/>
-      <c r="O55" s="18"/>
-      <c r="P55" s="18">
-        <v>6826</v>
-      </c>
-      <c r="Q55" s="18">
-        <v>5231</v>
+      <c r="L55" s="19">
+        <f t="shared" ref="L55:P55" si="13">SUM(L50:L54)</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="19">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N55" s="19">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O55" s="19">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="P55" s="19">
+        <f t="shared" si="13"/>
+        <v>15887</v>
+      </c>
+      <c r="Q55" s="19">
+        <f>SUM(Q50:Q54)</f>
+        <v>16937</v>
       </c>
       <c r="R55" s="18"/>
       <c r="S55" s="3"/>
@@ -2919,7 +2987,7 @@
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="C56" s="18"/>
       <c r="D56" s="18"/>
@@ -2930,35 +2998,24 @@
       <c r="I56" s="18"/>
       <c r="J56" s="18"/>
       <c r="K56" s="18"/>
-      <c r="L56" s="19">
-        <f t="shared" ref="L56:P56" si="13">SUM(L53:L55)</f>
-        <v>0</v>
-      </c>
-      <c r="M56" s="19">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N56" s="19">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="O56" s="19">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="P56" s="19">
-        <f t="shared" si="13"/>
-        <v>27727</v>
-      </c>
-      <c r="Q56" s="19">
-        <f>SUM(Q53:Q55)</f>
-        <v>28684</v>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
+      <c r="P56" s="18">
+        <v>15429</v>
+      </c>
+      <c r="Q56" s="18">
+        <v>17291</v>
       </c>
       <c r="R56" s="18"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B57" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="C57" s="18"/>
       <c r="D57" s="18"/>
       <c r="E57" s="18"/>
@@ -2972,15 +3029,19 @@
       <c r="M57" s="18"/>
       <c r="N57" s="18"/>
       <c r="O57" s="18"/>
-      <c r="P57" s="18"/>
-      <c r="Q57" s="18"/>
+      <c r="P57" s="18">
+        <v>5472</v>
+      </c>
+      <c r="Q57" s="18">
+        <v>6162</v>
+      </c>
       <c r="R57" s="18"/>
       <c r="S57" s="3"/>
       <c r="T57" s="3"/>
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B58" s="1" t="s">
-        <v>118</v>
+      <c r="B58" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="C58" s="18"/>
       <c r="D58" s="18"/>
@@ -2991,35 +3052,24 @@
       <c r="I58" s="18"/>
       <c r="J58" s="18"/>
       <c r="K58" s="18"/>
-      <c r="L58" s="19">
-        <f t="shared" ref="L58:P58" si="14">L52+L56</f>
-        <v>0</v>
-      </c>
-      <c r="M58" s="19">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N58" s="19">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O58" s="19">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="P58" s="19">
-        <f t="shared" si="14"/>
-        <v>43614</v>
-      </c>
-      <c r="Q58" s="19">
-        <f>Q52+Q56</f>
-        <v>45621</v>
+      <c r="L58" s="18"/>
+      <c r="M58" s="18"/>
+      <c r="N58" s="18"/>
+      <c r="O58" s="18"/>
+      <c r="P58" s="18">
+        <v>6826</v>
+      </c>
+      <c r="Q58" s="18">
+        <v>5231</v>
       </c>
       <c r="R58" s="18"/>
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B59" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="C59" s="18"/>
       <c r="D59" s="18"/>
       <c r="E59" s="18"/>
@@ -3029,20 +3079,35 @@
       <c r="I59" s="18"/>
       <c r="J59" s="18"/>
       <c r="K59" s="18"/>
-      <c r="L59" s="18"/>
-      <c r="M59" s="18"/>
-      <c r="N59" s="18"/>
-      <c r="O59" s="18"/>
-      <c r="P59" s="18"/>
-      <c r="Q59" s="18"/>
+      <c r="L59" s="19">
+        <f t="shared" ref="L59:P59" si="14">SUM(L56:L58)</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="19">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="N59" s="19">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="O59" s="19">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="P59" s="19">
+        <f t="shared" si="14"/>
+        <v>27727</v>
+      </c>
+      <c r="Q59" s="19">
+        <f>SUM(Q56:Q58)</f>
+        <v>28684</v>
+      </c>
       <c r="R59" s="18"/>
       <c r="S59" s="3"/>
       <c r="T59" s="3"/>
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B60" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="C60" s="18"/>
       <c r="D60" s="18"/>
       <c r="E60" s="18"/>
@@ -3056,17 +3121,16 @@
       <c r="M60" s="18"/>
       <c r="N60" s="18"/>
       <c r="O60" s="18"/>
-      <c r="P60" s="18">
-        <v>9266</v>
-      </c>
-      <c r="Q60" s="18">
-        <v>6835</v>
-      </c>
+      <c r="P60" s="18"/>
+      <c r="Q60" s="18"/>
       <c r="R60" s="18"/>
       <c r="S60" s="3"/>
       <c r="T60" s="3"/>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
+        <v>118</v>
+      </c>
       <c r="C61" s="18"/>
       <c r="D61" s="18"/>
       <c r="E61" s="18"/>
@@ -3076,20 +3140,35 @@
       <c r="I61" s="18"/>
       <c r="J61" s="18"/>
       <c r="K61" s="18"/>
-      <c r="L61" s="18"/>
-      <c r="M61" s="18"/>
-      <c r="N61" s="18"/>
-      <c r="O61" s="18"/>
-      <c r="P61" s="18"/>
-      <c r="Q61" s="18"/>
+      <c r="L61" s="19">
+        <f t="shared" ref="L61:P61" si="15">L55+L59</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="19">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N61" s="19">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O61" s="19">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="P61" s="19">
+        <f t="shared" si="15"/>
+        <v>43614</v>
+      </c>
+      <c r="Q61" s="19">
+        <f>Q55+Q59</f>
+        <v>45621</v>
+      </c>
       <c r="R61" s="18"/>
       <c r="S61" s="3"/>
       <c r="T61" s="3"/>
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B62" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="C62" s="18"/>
       <c r="D62" s="18"/>
       <c r="E62" s="18"/>
@@ -3099,35 +3178,20 @@
       <c r="I62" s="18"/>
       <c r="J62" s="18"/>
       <c r="K62" s="18"/>
-      <c r="L62" s="19">
-        <f t="shared" ref="L62:O62" si="15">L58+L60</f>
-        <v>0</v>
-      </c>
-      <c r="M62" s="19">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="N62" s="19">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O62" s="19">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P62" s="19">
-        <f t="shared" ref="P62" si="16">P58+P60</f>
-        <v>52880</v>
-      </c>
-      <c r="Q62" s="19">
-        <f>Q58+Q60</f>
-        <v>52456</v>
-      </c>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
+      <c r="P62" s="18"/>
+      <c r="Q62" s="18"/>
       <c r="R62" s="18"/>
       <c r="S62" s="3"/>
       <c r="T62" s="3"/>
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B63" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="C63" s="18"/>
       <c r="D63" s="18"/>
       <c r="E63" s="18"/>
@@ -3141,8 +3205,12 @@
       <c r="M63" s="18"/>
       <c r="N63" s="18"/>
       <c r="O63" s="18"/>
-      <c r="P63" s="18"/>
-      <c r="Q63" s="18"/>
+      <c r="P63" s="18">
+        <v>9266</v>
+      </c>
+      <c r="Q63" s="18">
+        <v>6835</v>
+      </c>
       <c r="R63" s="18"/>
       <c r="S63" s="3"/>
       <c r="T63" s="3"/>
@@ -3167,7 +3235,10 @@
       <c r="S64" s="3"/>
       <c r="T64" s="3"/>
     </row>
-    <row r="65" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="C65" s="18"/>
       <c r="D65" s="18"/>
       <c r="E65" s="18"/>
@@ -3177,17 +3248,35 @@
       <c r="I65" s="18"/>
       <c r="J65" s="18"/>
       <c r="K65" s="18"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="18"/>
-      <c r="N65" s="18"/>
-      <c r="O65" s="18"/>
-      <c r="P65" s="18"/>
-      <c r="Q65" s="18"/>
+      <c r="L65" s="19">
+        <f t="shared" ref="L65:O65" si="16">L61+L63</f>
+        <v>0</v>
+      </c>
+      <c r="M65" s="19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="N65" s="19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O65" s="19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P65" s="19">
+        <f t="shared" ref="P65" si="17">P61+P63</f>
+        <v>52880</v>
+      </c>
+      <c r="Q65" s="19">
+        <f>Q61+Q63</f>
+        <v>52456</v>
+      </c>
       <c r="R65" s="18"/>
       <c r="S65" s="3"/>
       <c r="T65" s="3"/>
     </row>
-    <row r="66" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="18"/>
       <c r="D66" s="18"/>
       <c r="E66" s="18"/>
@@ -3207,7 +3296,7 @@
       <c r="S66" s="3"/>
       <c r="T66" s="3"/>
     </row>
-    <row r="67" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="18"/>
       <c r="D67" s="18"/>
       <c r="E67" s="18"/>
@@ -3227,7 +3316,7 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
     </row>
-    <row r="68" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="18"/>
       <c r="D68" s="18"/>
       <c r="E68" s="18"/>
@@ -3247,7 +3336,7 @@
       <c r="S68" s="3"/>
       <c r="T68" s="3"/>
     </row>
-    <row r="69" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="18"/>
       <c r="D69" s="18"/>
       <c r="E69" s="18"/>
@@ -3267,7 +3356,7 @@
       <c r="S69" s="3"/>
       <c r="T69" s="3"/>
     </row>
-    <row r="70" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="18"/>
       <c r="D70" s="18"/>
       <c r="E70" s="18"/>
@@ -3287,7 +3376,7 @@
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
     </row>
-    <row r="71" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="18"/>
       <c r="D71" s="18"/>
       <c r="E71" s="18"/>
@@ -3307,7 +3396,7 @@
       <c r="S71" s="3"/>
       <c r="T71" s="3"/>
     </row>
-    <row r="72" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="18"/>
       <c r="D72" s="18"/>
       <c r="E72" s="18"/>
@@ -3327,7 +3416,7 @@
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
     </row>
-    <row r="73" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="18"/>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
@@ -3347,7 +3436,7 @@
       <c r="S73" s="3"/>
       <c r="T73" s="3"/>
     </row>
-    <row r="74" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="18"/>
       <c r="D74" s="18"/>
       <c r="E74" s="18"/>
@@ -3367,7 +3456,7 @@
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
     </row>
-    <row r="75" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="18"/>
       <c r="D75" s="18"/>
       <c r="E75" s="18"/>
@@ -3387,7 +3476,7 @@
       <c r="S75" s="3"/>
       <c r="T75" s="3"/>
     </row>
-    <row r="76" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="18"/>
       <c r="D76" s="18"/>
       <c r="E76" s="18"/>
@@ -3407,7 +3496,7 @@
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
     </row>
-    <row r="77" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="18"/>
       <c r="D77" s="18"/>
       <c r="E77" s="18"/>
@@ -3427,7 +3516,7 @@
       <c r="S77" s="3"/>
       <c r="T77" s="3"/>
     </row>
-    <row r="78" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C78" s="18"/>
       <c r="D78" s="18"/>
       <c r="E78" s="18"/>
@@ -3447,7 +3536,7 @@
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
     </row>
-    <row r="79" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C79" s="18"/>
       <c r="D79" s="18"/>
       <c r="E79" s="18"/>
@@ -3467,7 +3556,7 @@
       <c r="S79" s="3"/>
       <c r="T79" s="3"/>
     </row>
-    <row r="80" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="18"/>
       <c r="D80" s="18"/>
       <c r="E80" s="18"/>
@@ -3888,56 +3977,62 @@
       <c r="T100" s="3"/>
     </row>
     <row r="101" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3"/>
-      <c r="J101" s="3"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="3"/>
-      <c r="M101" s="3"/>
-      <c r="N101" s="3"/>
-      <c r="O101" s="3"/>
-      <c r="P101" s="3"/>
-      <c r="Q101" s="3"/>
-      <c r="R101" s="3"/>
+      <c r="C101" s="18"/>
+      <c r="D101" s="18"/>
+      <c r="E101" s="18"/>
+      <c r="F101" s="18"/>
+      <c r="G101" s="18"/>
+      <c r="H101" s="18"/>
+      <c r="I101" s="18"/>
+      <c r="J101" s="18"/>
+      <c r="K101" s="18"/>
+      <c r="L101" s="18"/>
+      <c r="M101" s="18"/>
+      <c r="N101" s="18"/>
+      <c r="O101" s="18"/>
+      <c r="P101" s="18"/>
+      <c r="Q101" s="18"/>
+      <c r="R101" s="18"/>
       <c r="S101" s="3"/>
       <c r="T101" s="3"/>
     </row>
     <row r="102" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="3"/>
-      <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
-      <c r="L102" s="3"/>
-      <c r="M102" s="3"/>
-      <c r="N102" s="3"/>
-      <c r="O102" s="3"/>
-      <c r="P102" s="3"/>
-      <c r="Q102" s="3"/>
-      <c r="R102" s="3"/>
+      <c r="C102" s="18"/>
+      <c r="D102" s="18"/>
+      <c r="E102" s="18"/>
+      <c r="F102" s="18"/>
+      <c r="G102" s="18"/>
+      <c r="H102" s="18"/>
+      <c r="I102" s="18"/>
+      <c r="J102" s="18"/>
+      <c r="K102" s="18"/>
+      <c r="L102" s="18"/>
+      <c r="M102" s="18"/>
+      <c r="N102" s="18"/>
+      <c r="O102" s="18"/>
+      <c r="P102" s="18"/>
+      <c r="Q102" s="18"/>
+      <c r="R102" s="18"/>
       <c r="S102" s="3"/>
       <c r="T102" s="3"/>
     </row>
     <row r="103" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="3"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3"/>
-      <c r="M103" s="3"/>
-      <c r="N103" s="3"/>
-      <c r="O103" s="3"/>
-      <c r="P103" s="3"/>
-      <c r="Q103" s="3"/>
-      <c r="R103" s="3"/>
+      <c r="C103" s="18"/>
+      <c r="D103" s="18"/>
+      <c r="E103" s="18"/>
+      <c r="F103" s="18"/>
+      <c r="G103" s="18"/>
+      <c r="H103" s="18"/>
+      <c r="I103" s="18"/>
+      <c r="J103" s="18"/>
+      <c r="K103" s="18"/>
+      <c r="L103" s="18"/>
+      <c r="M103" s="18"/>
+      <c r="N103" s="18"/>
+      <c r="O103" s="18"/>
+      <c r="P103" s="18"/>
+      <c r="Q103" s="18"/>
+      <c r="R103" s="18"/>
       <c r="S103" s="3"/>
       <c r="T103" s="3"/>
     </row>
@@ -7577,6 +7672,60 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
     </row>
+    <row r="306" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E306" s="3"/>
+      <c r="F306" s="3"/>
+      <c r="G306" s="3"/>
+      <c r="H306" s="3"/>
+      <c r="I306" s="3"/>
+      <c r="J306" s="3"/>
+      <c r="K306" s="3"/>
+      <c r="L306" s="3"/>
+      <c r="M306" s="3"/>
+      <c r="N306" s="3"/>
+      <c r="O306" s="3"/>
+      <c r="P306" s="3"/>
+      <c r="Q306" s="3"/>
+      <c r="R306" s="3"/>
+      <c r="S306" s="3"/>
+      <c r="T306" s="3"/>
+    </row>
+    <row r="307" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E307" s="3"/>
+      <c r="F307" s="3"/>
+      <c r="G307" s="3"/>
+      <c r="H307" s="3"/>
+      <c r="I307" s="3"/>
+      <c r="J307" s="3"/>
+      <c r="K307" s="3"/>
+      <c r="L307" s="3"/>
+      <c r="M307" s="3"/>
+      <c r="N307" s="3"/>
+      <c r="O307" s="3"/>
+      <c r="P307" s="3"/>
+      <c r="Q307" s="3"/>
+      <c r="R307" s="3"/>
+      <c r="S307" s="3"/>
+      <c r="T307" s="3"/>
+    </row>
+    <row r="308" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E308" s="3"/>
+      <c r="F308" s="3"/>
+      <c r="G308" s="3"/>
+      <c r="H308" s="3"/>
+      <c r="I308" s="3"/>
+      <c r="J308" s="3"/>
+      <c r="K308" s="3"/>
+      <c r="L308" s="3"/>
+      <c r="M308" s="3"/>
+      <c r="N308" s="3"/>
+      <c r="O308" s="3"/>
+      <c r="P308" s="3"/>
+      <c r="Q308" s="3"/>
+      <c r="R308" s="3"/>
+      <c r="S308" s="3"/>
+      <c r="T308" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{D291865D-AF1E-435E-8001-721FE7FD4466}"/>
